--- a/healthcare_forms/001_patient_feedback_form--healthcare_forms.xlsx
+++ b/healthcare_forms/001_patient_feedback_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -807,8 +807,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -836,12 +836,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'1_-_very_satisfied'}</t>
+          <t>1_-_very_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': '1 - Very Satisfied'}</t>
+          <t>1 - Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'2_-_somewhat_satisfied'}</t>
+          <t>2_-_somewhat_satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': '2 - Somewhat Satisfied'}</t>
+          <t>2 - Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'3_-_neutral'}</t>
+          <t>3_-_neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': '3 - Neutral'}</t>
+          <t>3 - Neutral</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'4_-_somewhat_dissatisfied'}</t>
+          <t>4_-_somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': '4 - Somewhat Dissatisfied'}</t>
+          <t>4 - Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'5_-_very_dissatisfied'}</t>
+          <t>5_-_very_dissatisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': '5 - Very Dissatisfied'}</t>
+          <t>5 - Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'1_-_excellent'}</t>
+          <t>1_-_excellent</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': '1 - Excellent'}</t>
+          <t>1 - Excellent</t>
         </is>
       </c>
     </row>
@@ -938,12 +938,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'2_-_good'}</t>
+          <t>2_-_good</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': '2 - Good'}</t>
+          <t>2 - Good</t>
         </is>
       </c>
     </row>
@@ -955,12 +955,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'3_-_fair'}</t>
+          <t>3_-_fair</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': '3 - Fair'}</t>
+          <t>3 - Fair</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'4_-_poor'}</t>
+          <t>4_-_poor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': '4 - Poor'}</t>
+          <t>4 - Poor</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'1_-_very_clean'}</t>
+          <t>1_-_very_clean</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': '1 - Very Clean'}</t>
+          <t>1 - Very Clean</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'2_-_somewhat_clean'}</t>
+          <t>2_-_somewhat_clean</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': '2 - Somewhat Clean'}</t>
+          <t>2 - Somewhat Clean</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'3_-_neutral'}</t>
+          <t>3_-_neutral</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': '3 - Neutral'}</t>
+          <t>3 - Neutral</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'4_-_somewhat_dirty'}</t>
+          <t>4_-_somewhat_dirty</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': '4 - Somewhat Dirty'}</t>
+          <t>4 - Somewhat Dirty</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'5_-_very_dirty'}</t>
+          <t>5_-_very_dirty</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': '5 - Very Dirty'}</t>
+          <t>5 - Very Dirty</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
